--- a/Output/Quality_Checks/by-year/2005/Q1/MEX_2005_ENOE_V01_M_V06_A_GLD_ALL_Q-Checks.xlsx
+++ b/Output/Quality_Checks/by-year/2005/Q1/MEX_2005_ENOE_V01_M_V06_A_GLD_ALL_Q-Checks.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f3d9369a3ab00f0/IOR/Projects/Y2025/FY25_MEX_MinimumWage/ENOE_PANEL/Output/Quality_Checks/by-year/2005/Q1/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_305BA6FF8804FA76BCC93207E6012D16618CC547" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1C760CE-2CEC-744F-8214-40A2E85F9CEC}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Static" sheetId="1" r:id="rId2"/>
+    <sheet name="Static" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="483" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="180">
   <si>
     <t>Overall</t>
   </si>
@@ -558,8 +565,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -581,27 +588,364 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E161"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.5" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -631,7 +975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -646,7 +990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -661,7 +1005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -676,7 +1020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -691,7 +1035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -706,7 +1050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -721,7 +1065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -736,7 +1080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -751,7 +1095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -766,7 +1110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -781,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -796,7 +1140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -811,7 +1155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -826,7 +1170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -841,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -856,7 +1200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -871,7 +1215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -886,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -901,7 +1245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -916,7 +1260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -931,7 +1275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -946,7 +1290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -961,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -976,7 +1320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -991,7 +1335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1096,7 +1440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1111,7 +1455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +1485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1186,7 +1530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -1201,7 +1545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -1216,7 +1560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -1231,7 +1575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -1261,7 +1605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -1276,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -1291,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -1366,7 +1710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -1381,7 +1725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -1396,7 +1740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +1755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -1426,7 +1770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -1441,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1456,7 +1800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -1471,7 +1815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -1486,7 +1830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -1516,7 +1860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -1591,7 +1935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -1606,7 +1950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -1681,7 +2025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -1696,7 +2040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>0</v>
       </c>
@@ -1711,7 +2055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>0</v>
       </c>
@@ -1726,7 +2070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -1741,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -1756,7 +2100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -1771,7 +2115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -1786,7 +2130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -1801,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -1816,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>0</v>
       </c>
@@ -1831,7 +2175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -1846,7 +2190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -1861,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -1876,7 +2220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>0</v>
       </c>
@@ -1891,7 +2235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +2250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>0</v>
       </c>
@@ -1921,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>0</v>
       </c>
@@ -1936,7 +2280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>0</v>
       </c>
@@ -1951,7 +2295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>0</v>
       </c>
@@ -1966,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>0</v>
       </c>
@@ -1981,7 +2325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>0</v>
       </c>
@@ -1996,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>0</v>
       </c>
@@ -2011,7 +2355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>0</v>
       </c>
@@ -2026,7 +2370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>0</v>
       </c>
@@ -2041,7 +2385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>0</v>
       </c>
@@ -2056,7 +2400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>0</v>
       </c>
@@ -2071,7 +2415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>0</v>
       </c>
@@ -2086,7 +2430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>0</v>
       </c>
@@ -2101,7 +2445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>0</v>
       </c>
@@ -2116,7 +2460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>0</v>
       </c>
@@ -2131,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -2146,7 +2490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>0</v>
       </c>
@@ -2161,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>0</v>
       </c>
@@ -2176,7 +2520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>0</v>
       </c>
@@ -2191,7 +2535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>0</v>
       </c>
@@ -2206,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>0</v>
       </c>
@@ -2221,7 +2565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>0</v>
       </c>
@@ -2236,7 +2580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>0</v>
       </c>
@@ -2251,7 +2595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>0</v>
       </c>
@@ -2266,7 +2610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>0</v>
       </c>
@@ -2281,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>0</v>
       </c>
@@ -2296,7 +2640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>0</v>
       </c>
@@ -2311,7 +2655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>0</v>
       </c>
@@ -2326,7 +2670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>0</v>
       </c>
@@ -2341,7 +2685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>0</v>
       </c>
@@ -2356,7 +2700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>0</v>
       </c>
@@ -2371,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>0</v>
       </c>
@@ -2386,7 +2730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>0</v>
       </c>
@@ -2401,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>0</v>
       </c>
@@ -2416,7 +2760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>0</v>
       </c>
@@ -2431,7 +2775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -2446,7 +2790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>0</v>
       </c>
@@ -2461,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>0</v>
       </c>
@@ -2476,7 +2820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>0</v>
       </c>
@@ -2491,7 +2835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -2506,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>0</v>
       </c>
@@ -2521,7 +2865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>0</v>
       </c>
@@ -2536,7 +2880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>0</v>
       </c>
@@ -2551,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>0</v>
       </c>
@@ -2566,7 +2910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>0</v>
       </c>
@@ -2581,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>0</v>
       </c>
@@ -2611,7 +2955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -2626,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>0</v>
       </c>
@@ -2641,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>0</v>
       </c>
@@ -2656,7 +3000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>0</v>
       </c>
@@ -2671,7 +3015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>0</v>
       </c>
@@ -2686,7 +3030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -2701,7 +3045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>0</v>
       </c>
@@ -2716,7 +3060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>0</v>
       </c>
@@ -2731,7 +3075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>0</v>
       </c>
@@ -2746,7 +3090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>0</v>
       </c>
@@ -2761,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -2776,7 +3120,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>0</v>
       </c>
@@ -2791,7 +3135,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>0</v>
       </c>
@@ -2806,7 +3150,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>0</v>
       </c>
@@ -2821,7 +3165,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -2836,7 +3180,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>0</v>
       </c>
@@ -2847,13 +3191,13 @@
         <v>170</v>
       </c>
       <c r="D150" s="1">
-        <v>0.0034368294291198254</v>
+        <v>3.4368294291198254E-3</v>
       </c>
       <c r="E150" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>0</v>
       </c>
@@ -2864,13 +3208,13 @@
         <v>171</v>
       </c>
       <c r="D151" s="1">
-        <v>0.025196896865963936</v>
+        <v>2.5196896865963936E-2</v>
       </c>
       <c r="E151" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>0</v>
       </c>
@@ -2881,13 +3225,13 @@
         <v>171</v>
       </c>
       <c r="D152" s="1">
-        <v>0.025196896865963936</v>
+        <v>2.5196896865963936E-2</v>
       </c>
       <c r="E152" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>1</v>
       </c>
@@ -2898,13 +3242,13 @@
         <v>172</v>
       </c>
       <c r="D153" s="1">
-        <v>0.0054045729339122772</v>
+        <v>5.4045729339122772E-3</v>
       </c>
       <c r="E153" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>1</v>
       </c>
@@ -2921,7 +3265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>2</v>
       </c>
@@ -2938,7 +3282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>3</v>
       </c>
@@ -2953,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>3</v>
       </c>
@@ -2970,7 +3314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>3</v>
       </c>
@@ -2987,7 +3331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -2998,13 +3342,13 @@
         <v>177</v>
       </c>
       <c r="D159" s="1">
-        <v>0.0083432001993060112</v>
+        <v>8.3432001993060112E-3</v>
       </c>
       <c r="E159" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -3015,13 +3359,13 @@
         <v>178</v>
       </c>
       <c r="D160" s="1">
-        <v>0.00390625</v>
+        <v>3.90625E-3</v>
       </c>
       <c r="E160" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -3032,12 +3376,13 @@
         <v>179</v>
       </c>
       <c r="D161" s="1">
-        <v>0.011254019103944302</v>
+        <v>1.1254019103944302E-2</v>
       </c>
       <c r="E161" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>